--- a/src/assets/static files/block_unblock_line.xlsx
+++ b/src/assets/static files/block_unblock_line.xlsx
@@ -15,16 +15,11 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="CalcA1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>User Name</t>
   </si>
@@ -36,13 +31,22 @@
   </si>
   <si>
     <t>Is Block</t>
+  </si>
+  <si>
+    <t>Shubham Bhartiya</t>
+  </si>
+  <si>
+    <t>FPL-00000000001</t>
+  </si>
+  <si>
+    <t>Yes</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -53,6 +57,12 @@
       <color rgb="FF1D1C1D"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -72,16 +82,19 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -380,6 +393,20 @@
         <v>3</v>
       </c>
     </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="3">
+        <v>8080758758</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="D4" s="1"/>
     </row>
